--- a/reports/jobs_2026-07-21.xlsx
+++ b/reports/jobs_2026-07-21.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Openings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -488,8 +493,570 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAP FICO Consultant in UAE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Senior SAP Finance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Uae Job Alert</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-4ea378090edfa2cd75935ec488dce1cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SAP FICO Consultant in UAE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAP Finance Specialist</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Talents Of Endearment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-98bbee26285fcb2051addbb4cee0584d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SAP FICO Consultant in UAE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Financial Accounting Intern — SAP, AR/AP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Merz Aesthetics GmbH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-67772766bb988fc53f0bba28e88ded63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Senior Accountant &amp; Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tresta International FZE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.indeed.com/viewjob?jk=e919a50553fc033c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Accounts Receivable Analyst</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Accounts Receivable Analyst [METAP] - TikTok MENA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-cdeed1c0fa23a5c7a0b0a33068e41e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Remote FP&amp;A Data Analyst — Automation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MIRA CONSTRUCTION L.L.C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-c00e9d4cbb4974ab67cb5c500ce0a629</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Payments Analyst</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Keyper</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-b7a967e9e344ac786550ac697eddbb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Financial Planning  and  Analysis FP and A Analyst</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ghassan Aboud Holding</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-5199-f6f2d24dd91c83ac786faf878bf7ff6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Regional Finance Analyst: Drive Forecasts</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Careers at UAE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-7c67864332d43e9bafd639cae52e3727</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Financial Analyst — Insights for Budgeting</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hyphen Connect Limited</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-ce67992b0fe94568bd92079868704ca8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Senior Finacle Core Banking Finance Analyst</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VAM Systems</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-d9520c85012b5d4b260e23731e44d13f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Regional FP&amp;A Analyst: Strategic Forecasting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Careers at UAE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-936319a047ad631b56eac1c3dc8083cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Strategic Financial Analyst: Forecasts</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WSP in the Middle East</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-25bbe8f358a96493713afef4f74175d6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I14"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/jobs_2026-07-21.xlsx
+++ b/reports/jobs_2026-07-21.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Openings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,11 @@
           <t>Uae Job Alert</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -548,7 +552,11 @@
           <t>Talents Of Endearment</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -587,7 +595,11 @@
           <t>Merz Aesthetics GmbH</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -613,17 +625,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senior Accountant &amp; Financial Analyst</t>
+          <t>Accountant-Accounts Receivable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tresta International FZE</t>
+          <t>System8 Logistics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -649,24 +661,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://ae.indeed.com/viewjob?jk=e919a50553fc033c</t>
+          <t>https://ae.indeed.com/viewjob?jk=fa3e11f13b25110f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accounts Receivable Analyst</t>
+          <t>Hiring for a Senior Accountant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Accounts Receivable Analyst [METAP] - TikTok MENA</t>
+          <t>Mashriq Elite Real Estate Development L.L.C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -687,29 +699,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-cdeed1c0fa23a5c7a0b0a33068e41e0b</t>
+          <t>https://ae.indeed.com/viewjob?jk=fb485b5b5074e8df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Remote FP&amp;A Data Analyst — Automation</t>
+          <t>Remote Senior Payroll Accountant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIRA CONSTRUCTION L.L.C</t>
+          <t>Remotedxb</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -735,24 +747,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-c00e9d4cbb4974ab67cb5c500ce0a629</t>
+          <t>https://ae.trabajo.org/job-3339-9548ec5b38fa88fee81f8e524b088468</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Payments Analyst</t>
+          <t>Female Accountant/ Arabic Speaker/Shipping</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Keyper</t>
+          <t>Glow Shipping Lines LLC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,29 +785,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-b7a967e9e344ac786550ac697eddbb2d</t>
+          <t>https://ae.indeed.com/viewjob?jk=1a699468a1bf9987</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Planning  and  Analysis FP and A Analyst</t>
+          <t>Accounts Associate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ghassan Aboud Holding</t>
+          <t>TFAB Accounting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -816,29 +828,29 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-5199-f6f2d24dd91c83ac786faf878bf7ff6e</t>
+          <t>https://ae.linkedin.com/jobs/view/accounts-associate-at-tfab-accounting-4440122324</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Regional Finance Analyst: Drive Forecasts</t>
+          <t>[Hiring] Administrator / Accountant Ajman UAE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Careers at UAE</t>
+          <t>confidential</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -859,29 +871,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Jooble</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-7c67864332d43e9bafd639cae52e3727</t>
+          <t>https://ae.jooble.org/jdp/-4193650803750160188</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Financial Analyst — Insights for Budgeting</t>
+          <t>Entry-Level Accountant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hyphen Connect Limited</t>
+          <t>Visa Boards</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -907,24 +919,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-ce67992b0fe94568bd92079868704ca8</t>
+          <t>https://ae.trabajo.org/job-3339-26ffb27f6a2b4848d85ab40a576058e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Senior Finacle Core Banking Finance Analyst</t>
+          <t>Accountant (Construction)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VAM Systems</t>
+          <t>Reliant Steel Construction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -945,29 +957,29 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-d9520c85012b5d4b260e23731e44d13f</t>
+          <t>https://ae.indeed.com/viewjob?jk=30ed666f626feb59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Regional FP&amp;A Analyst: Strategic Forecasting</t>
+          <t>Statutory Accountant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Careers at UAE</t>
+          <t>applydubaijob.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -993,24 +1005,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-936319a047ad631b56eac1c3dc8083cb</t>
+          <t>https://ae.trabajo.org/job-3339-4a64cd9ea51b6b0f6f8bad92bbe1e69b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Financial Analyst in Sharjah</t>
+          <t>Accountant in Dubai</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Strategic Financial Analyst: Forecasts</t>
+          <t>CPA AI Trainer: Accounting Precision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WSP in the Middle East</t>
+          <t>Remotedxb</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,12 +1048,442 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>https://ae.trabajo.org/job-3339-2405ed3bbb5437bd0a6e2364a792d053</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Senior Accountant &amp; Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tresta International FZE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.indeed.com/viewjob?jk=e919a50553fc033c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Accounts Receivable Analyst</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Accounts Receivable Analyst [METAP] - TikTok MENA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-cdeed1c0fa23a5c7a0b0a33068e41e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Remote FP&amp;A Data Analyst — Automation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MIRA CONSTRUCTION L.L.C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-c00e9d4cbb4974ab67cb5c500ce0a629</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Payments Analyst</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Keyper</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-b7a967e9e344ac786550ac697eddbb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Regional Finance Analyst: Drive Forecasts</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Careers at UAE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-7c67864332d43e9bafd639cae52e3727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Financial Analyst — Insights for Budgeting</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hyphen Connect Limited</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-ce67992b0fe94568bd92079868704ca8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Senior Finacle Core Banking Finance Analyst</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VAM Systems</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-d9520c85012b5d4b260e23731e44d13f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Regional FP&amp;A Analyst: Strategic Forecasting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Careers at UAE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-936319a047ad631b56eac1c3dc8083cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Strategic Financial Analyst: Forecasts</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WSP in the Middle East</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>https://ae.trabajo.org/job-3339-25bbe8f358a96493713afef4f74175d6</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Financial Analyst in Sharjah</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Development &amp; Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AE7</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Trabajo.org</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://ae.trabajo.org/job-3339-f240be77a3049e02d6ae40b342e3fa1b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -1056,6 +1498,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
